--- a/data/personalia/IV TNK.xlsx
+++ b/data/personalia/IV TNK.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC1878E-1B09-4D8A-9A03-17F4F5AA20AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B04B96A-5A92-4BDE-AA4D-5DC85E573275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="369">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,6 +172,114 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
     <t>VACANT</t>
   </si>
   <si>
@@ -172,9 +289,6 @@
     <t>Pelaksana Perencanaan Teknis</t>
   </si>
   <si>
-    <t>Teknisi</t>
-  </si>
-  <si>
     <t>IV TNK</t>
   </si>
   <si>
@@ -184,6 +298,9 @@
     <t>PLT Manager STE Divre IV Tnk</t>
   </si>
   <si>
+    <t>PMP.090681.127234</t>
+  </si>
+  <si>
     <t>SUGENG</t>
   </si>
   <si>
@@ -196,6 +313,9 @@
     <t>QC STL IVB Nrr</t>
   </si>
   <si>
+    <t>PMP.081274.00987</t>
+  </si>
+  <si>
     <t>ARIF WAHYUNIR</t>
   </si>
   <si>
@@ -208,6 +328,9 @@
     <t>QC STL IVD Pgg</t>
   </si>
   <si>
+    <t>PMP.040770.00890</t>
+  </si>
+  <si>
     <t>INDRA PRASETIA</t>
   </si>
   <si>
@@ -220,12 +343,18 @@
     <t>AM Kegiatan dan Pembiyaan Divre IV Tnk</t>
   </si>
   <si>
+    <t>PMP.17051987.30099</t>
+  </si>
+  <si>
     <t>KUSUMA ABDILLAH</t>
   </si>
   <si>
     <t>AM Perencanaan Teknis Divre IV Tnk</t>
   </si>
   <si>
+    <t>PMP.160888.125169</t>
+  </si>
+  <si>
     <t>FEBRIZAH ARASWITHA</t>
   </si>
   <si>
@@ -235,15 +364,27 @@
     <t>DITA ANGGERAINI</t>
   </si>
   <si>
+    <t>PRP.290593.46837</t>
+  </si>
+  <si>
     <t>NURUL HANDAYANI</t>
   </si>
   <si>
+    <t>PRP.210595.128221</t>
+  </si>
+  <si>
     <t>IRFAN WAHYUDI</t>
   </si>
   <si>
+    <t>PRP. 281195. 39874</t>
+  </si>
+  <si>
     <t>DIDIK KURNIAWAN</t>
   </si>
   <si>
+    <t>PRP.261287.45266</t>
+  </si>
+  <si>
     <t>SUGIHARTO</t>
   </si>
   <si>
@@ -259,12 +400,18 @@
     <t>Supervisor Perbaikan Workshop Sintelis Tnk</t>
   </si>
   <si>
+    <t>PRP.170384.128690</t>
+  </si>
+  <si>
     <t>EDO SULISTIYANTO</t>
   </si>
   <si>
     <t>Kepala Subunit Rekayasa UPT Workshop</t>
   </si>
   <si>
+    <t>PRP.27071990.29611</t>
+  </si>
+  <si>
     <t>MUHAMMAD SALIM IKHWAN</t>
   </si>
   <si>
@@ -274,9 +421,15 @@
     <t>POGGI RAHMAN</t>
   </si>
   <si>
+    <t>PRP.230400.75621</t>
+  </si>
+  <si>
     <t>MUHAMMAD AL AMIEN LUBIS</t>
   </si>
   <si>
+    <t>PRP.100998.62399</t>
+  </si>
+  <si>
     <t>ASRORUDIN RAIS</t>
   </si>
   <si>
@@ -292,39 +445,63 @@
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C IV.1 Thn</t>
   </si>
   <si>
+    <t>PRP.310182.00732</t>
+  </si>
+  <si>
     <t>BAGUS SETIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C IV.1 Thn</t>
   </si>
   <si>
+    <t>PRP.070893.00695</t>
+  </si>
+  <si>
     <t>M DAFFA MAULANA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.1 Thn</t>
   </si>
   <si>
+    <t>PRP.090500.70413</t>
+  </si>
+  <si>
     <t>ANTONIUS JANUARIO</t>
   </si>
   <si>
+    <t>PRP.170102.73669</t>
+  </si>
+  <si>
     <t>ANGGA APRIANSYAH</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.1 Thn</t>
   </si>
   <si>
+    <t>PRP.230693.53313</t>
+  </si>
+  <si>
     <t>ANDHIKA PRATAMA NABABAN</t>
   </si>
   <si>
+    <t>PRP.110504.74227</t>
+  </si>
+  <si>
     <t>JOVINTO FLYANO</t>
   </si>
   <si>
+    <t>PRP.220101.74153</t>
+  </si>
+  <si>
     <t>IHSAN AL HAKIM</t>
   </si>
   <si>
     <t>SETYO ADI PERDANA</t>
   </si>
   <si>
+    <t>PRP.220702.73675</t>
+  </si>
+  <si>
     <t>GALIH PINARYOGA</t>
   </si>
   <si>
@@ -334,48 +511,81 @@
     <t>IV.2 Tnk</t>
   </si>
   <si>
+    <t>PRP.180493.48851</t>
+  </si>
+  <si>
+    <t>PMP.180493.66244</t>
+  </si>
+  <si>
     <t>PRASETYA ADE PUTRA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B IV.2 Tnk</t>
   </si>
   <si>
+    <t>PRP.29101990.32325</t>
+  </si>
+  <si>
     <t>DODY SAPUTRA D.</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis IV.2 Tnk</t>
   </si>
   <si>
+    <t>PRP.100491.128223</t>
+  </si>
+  <si>
     <t>KHAIRUL AMIN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.2 Tnk</t>
   </si>
   <si>
+    <t>PRP. 070992. 40888</t>
+  </si>
+  <si>
     <t>SYAIFUL ANWAR</t>
   </si>
   <si>
     <t>JUAN TRI WINDANU</t>
   </si>
   <si>
+    <t>PRP.290396.45265</t>
+  </si>
+  <si>
     <t>ALDI DWI WAHYU</t>
   </si>
   <si>
+    <t>PRP.260695.122287</t>
+  </si>
+  <si>
     <t>MARIYO EFFENDI</t>
   </si>
   <si>
+    <t>PRP.280396.41455</t>
+  </si>
+  <si>
     <t>HARRY PRASETYO KURNIAWAN</t>
   </si>
   <si>
+    <t>PRP.010997.74152</t>
+  </si>
+  <si>
     <t>BENI SUWARDANI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.2 Tnk</t>
   </si>
   <si>
+    <t>PRP.171191.00731</t>
+  </si>
+  <si>
     <t>MUHAMMAD FATHIN FADHIL</t>
   </si>
   <si>
+    <t>PRP.231202.73672</t>
+  </si>
+  <si>
     <t>UPT Resor Sintelis Kelas C IV.3 Rjs</t>
   </si>
   <si>
@@ -388,48 +598,81 @@
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C IV.3 Rjs</t>
   </si>
   <si>
+    <t>PRP.270584.00773</t>
+  </si>
+  <si>
     <t>ABDUL RAHMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C IV.3 Rjs</t>
   </si>
   <si>
+    <t>PRP.290990.128462</t>
+  </si>
+  <si>
     <t>WINDU PRAHASTA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.3 Rjs</t>
   </si>
   <si>
+    <t>PRP.100789.39883</t>
+  </si>
+  <si>
     <t>TRI SATRIA WIBAWA</t>
   </si>
   <si>
+    <t>PRP.030302.72850</t>
+  </si>
+  <si>
     <t>HAFIZ HIDAYAH AMRIVI</t>
   </si>
   <si>
+    <t>PRP.280403.72847</t>
+  </si>
+  <si>
     <t>MOHAMMAD ILHAM DWI ARIEF PURNAMA</t>
   </si>
   <si>
+    <t>PRP.080402.72848</t>
+  </si>
+  <si>
     <t>ZERI ANGGARA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.3 Rjs</t>
   </si>
   <si>
+    <t>PRP. 060692.40889</t>
+  </si>
+  <si>
     <t>EKO ADI KURNIAWAN</t>
   </si>
   <si>
+    <t>PRP.150391.45071</t>
+  </si>
+  <si>
     <t>MINDO SUPARTA</t>
   </si>
   <si>
+    <t>PRP.270796.62691</t>
+  </si>
+  <si>
     <t>TRIO SUSANTO</t>
   </si>
   <si>
+    <t>PRP.030591.45166</t>
+  </si>
+  <si>
     <t>SURYA SAFRUDIN</t>
   </si>
   <si>
     <t>Kepala UPT Resor Sintelis IV.4 Kb</t>
   </si>
   <si>
+    <t>PMP.030990.65326</t>
+  </si>
+  <si>
     <t>ASORI</t>
   </si>
   <si>
@@ -439,39 +682,66 @@
     <t>IV.4 Kb</t>
   </si>
   <si>
+    <t>PRP.290886.00779</t>
+  </si>
+  <si>
     <t>AGUS WINARTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Kelas C IV.4 Kb</t>
   </si>
   <si>
+    <t>PRP.261270.128269</t>
+  </si>
+  <si>
     <t>PARMONO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.4 Kb</t>
   </si>
   <si>
+    <t>PRP.101183.00778</t>
+  </si>
+  <si>
     <t>PANJI ASHARI FIRMAN</t>
   </si>
   <si>
+    <t>PRP. 030394. 39882</t>
+  </si>
+  <si>
     <t>RENALDI PERMANA</t>
   </si>
   <si>
+    <t>PRP. 060397. 39879</t>
+  </si>
+  <si>
     <t>MUHAMMAD PUNGUT</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.4 Kb</t>
   </si>
   <si>
+    <t>PRP. 261292. 39881</t>
+  </si>
+  <si>
     <t>ADI KURNIAWAN</t>
   </si>
   <si>
+    <t>PRP.100200.67473</t>
+  </si>
+  <si>
     <t>BAYU SEGARA</t>
   </si>
   <si>
+    <t>PRP.180698.70414</t>
+  </si>
+  <si>
     <t>ADITYA NOUVANT</t>
   </si>
   <si>
+    <t>PRP.120403.71440</t>
+  </si>
+  <si>
     <t>RANGGA ERLAN SANDY</t>
   </si>
   <si>
@@ -481,12 +751,18 @@
     <t>IV.5 Nrr</t>
   </si>
   <si>
+    <t>PRP.240888.128245</t>
+  </si>
+  <si>
     <t>EDWIN WINATA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C IV.5 Nrr</t>
   </si>
   <si>
+    <t>PRP.190791.00776</t>
+  </si>
+  <si>
     <t>BOBBY ARMAND</t>
   </si>
   <si>
@@ -499,30 +775,48 @@
     <t>PNC Perbaikan UPT Resor STL IV.5 Nrr</t>
   </si>
   <si>
+    <t>PRP.240577.00780</t>
+  </si>
+  <si>
     <t>RISMA ANDI SETIANTO</t>
   </si>
   <si>
     <t>MUHAMAD IQBAL</t>
   </si>
   <si>
+    <t>PRP.260601.74154</t>
+  </si>
+  <si>
     <t>AHMAD KABIER</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.5 Nrr</t>
   </si>
   <si>
+    <t>PRP. 270492. 39876</t>
+  </si>
+  <si>
     <t>HENDRA PAISAL</t>
   </si>
   <si>
+    <t>PRP. 110392. 39877</t>
+  </si>
+  <si>
     <t>MUBDIYAN FAJARENSAH</t>
   </si>
   <si>
     <t>M FARHAN PERDANA PUTRA</t>
   </si>
   <si>
+    <t>PRP.280801.73671</t>
+  </si>
+  <si>
     <t>DENY SYAPUTRA</t>
   </si>
   <si>
+    <t>PRP.261299.74151</t>
+  </si>
+  <si>
     <t>CHECEP NELLA HERTANTO</t>
   </si>
   <si>
@@ -532,12 +826,18 @@
     <t>IV.6 Mp</t>
   </si>
   <si>
+    <t>PMP.090889.67647</t>
+  </si>
+  <si>
     <t>JONI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B IV.6 Mp</t>
   </si>
   <si>
+    <t>PRP.270775.00701</t>
+  </si>
+  <si>
     <t>AGUS FITRI YANTO</t>
   </si>
   <si>
@@ -550,33 +850,57 @@
     <t>PNC Perbaikan UPT Resor STL IV.6 Mp</t>
   </si>
   <si>
+    <t>PRP. 170892. 38996</t>
+  </si>
+  <si>
     <t>WASKITO</t>
   </si>
   <si>
+    <t>PRP.28021989.33797</t>
+  </si>
+  <si>
     <t>HARUN</t>
   </si>
   <si>
+    <t>PRP.190387.41454</t>
+  </si>
+  <si>
     <t>ROBBY SEPTIAN</t>
   </si>
   <si>
+    <t>PRP.020998.74237</t>
+  </si>
+  <si>
     <t>FERRY TRI SETYA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.6 Mp</t>
   </si>
   <si>
+    <t>PRP. 051192.40885</t>
+  </si>
+  <si>
     <t>MUHAMMAD RIFQI SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.230797.74702</t>
+  </si>
+  <si>
     <t>DIMAS ADITIYO</t>
   </si>
   <si>
     <t>WAHYU DWI ANTORO</t>
   </si>
   <si>
+    <t>PRP.080202.71444</t>
+  </si>
+  <si>
     <t>MUHAMMAD HAFIDZ</t>
   </si>
   <si>
+    <t>PRP.091202.76820</t>
+  </si>
+  <si>
     <t>UPT Resor Sintelis Kelas B IV.7 Bta</t>
   </si>
   <si>
@@ -589,48 +913,81 @@
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B IV.7 Bta</t>
   </si>
   <si>
+    <t>PRP.030488.128222</t>
+  </si>
+  <si>
     <t>YUGO HALILINTAR</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B IV.7 Bta</t>
   </si>
   <si>
+    <t>PRP.011090.128506</t>
+  </si>
+  <si>
     <t>AAN HANDOKO OKTYAWAN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.7 Bta</t>
   </si>
   <si>
+    <t>PRP.171087.00741</t>
+  </si>
+  <si>
     <t>RUDIYANTO</t>
   </si>
   <si>
     <t>MUHAMMAD HASNUL</t>
   </si>
   <si>
+    <t>PRP.310704.74156</t>
+  </si>
+  <si>
     <t>ARIAN FACHRI</t>
   </si>
   <si>
+    <t>PRP.080302.74701</t>
+  </si>
+  <si>
     <t>MUHAMAD ANDIKA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.7 Bta</t>
   </si>
   <si>
+    <t>PRP.220298.122043</t>
+  </si>
+  <si>
     <t>ANDI SUSANTO</t>
   </si>
   <si>
+    <t>PRP.121078.00742</t>
+  </si>
+  <si>
     <t>ANDREAS SIREGAR</t>
   </si>
   <si>
+    <t>PRP. 220493. 40887</t>
+  </si>
+  <si>
     <t>RYO PAKUSADEWO</t>
   </si>
   <si>
+    <t>PRP.020900.62692</t>
+  </si>
+  <si>
     <t>ILHAM MUKSONI</t>
   </si>
   <si>
+    <t>PRP.301198.74791</t>
+  </si>
+  <si>
     <t>WAHYU HARRIZKI</t>
   </si>
   <si>
+    <t>PRP.110696.74157</t>
+  </si>
+  <si>
     <t>WAWAN SUBIANTORO</t>
   </si>
   <si>
@@ -640,6 +997,9 @@
     <t>IV.8 Pnw</t>
   </si>
   <si>
+    <t>PMP.280273.72149</t>
+  </si>
+  <si>
     <t>PARNINGOTAN TUA DANIEL S.</t>
   </si>
   <si>
@@ -652,36 +1012,63 @@
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C IV.8 Pnw</t>
   </si>
   <si>
+    <t>PRP.170989.00784</t>
+  </si>
+  <si>
     <t>DWI CHANDRA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.8 Pnw</t>
   </si>
   <si>
+    <t>PRP.310594.47459</t>
+  </si>
+  <si>
     <t>WIDI KATAMSU</t>
   </si>
   <si>
+    <t>PRP. 111195. 38781</t>
+  </si>
+  <si>
     <t>YOGIE DWI PUTRA</t>
   </si>
   <si>
+    <t>PRP.140700.74703</t>
+  </si>
+  <si>
     <t>MUHAMMAD HAFIZD FATURRAHMAN</t>
   </si>
   <si>
+    <t>PRP.190402.74155</t>
+  </si>
+  <si>
     <t>ADRIAN HALIM</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.8 Pnw</t>
   </si>
   <si>
+    <t>PRP.010293.53314</t>
+  </si>
+  <si>
     <t>ROHENDI MAHARDIKA</t>
   </si>
   <si>
+    <t>PRP. 130393. 38995</t>
+  </si>
+  <si>
     <t>TATA ARYA RIVANKA</t>
   </si>
   <si>
+    <t>PRP.071199.66246</t>
+  </si>
+  <si>
     <t>MUHAMMAD ALFA RIZI</t>
   </si>
   <si>
+    <t>PRP.250902.72849</t>
+  </si>
+  <si>
     <t>YAYAN PANCA SAPUTRA</t>
   </si>
   <si>
@@ -691,364 +1078,73 @@
     <t>IV.9 Pgg</t>
   </si>
   <si>
+    <t>PMP.130190.71596</t>
+  </si>
+  <si>
     <t>MUHAMMAD HARIS SUKRI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C IV.9 Pgg</t>
   </si>
   <si>
+    <t>PRP. 120493. 38780</t>
+  </si>
+  <si>
     <t>UNTUNG ANUGRAHA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C IV.9 Pgg</t>
   </si>
   <si>
+    <t>PRP.190986.00744</t>
+  </si>
+  <si>
     <t>IMAN MUTAKIN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL IV.9 Pgg</t>
   </si>
   <si>
+    <t>PRP. 300987. 39473</t>
+  </si>
+  <si>
     <t>FILTRA GAMU DIANATA</t>
   </si>
   <si>
+    <t>PRP.231003.72846</t>
+  </si>
+  <si>
     <t>RIZKY PRIMA MARHEINDRA</t>
   </si>
   <si>
+    <t>PRP.200302.71443</t>
+  </si>
+  <si>
     <t>BAMBANG YULISTYANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL IV.9 Pgg</t>
   </si>
   <si>
+    <t>PRP.230788.00785</t>
+  </si>
+  <si>
     <t>SUPRIYADI</t>
   </si>
   <si>
+    <t>PRP.120191.53311</t>
+  </si>
+  <si>
     <t>KEVIN VALENDRA</t>
   </si>
   <si>
+    <t>PRP.140204.73670</t>
+  </si>
+  <si>
     <t>BOBY ARIYANTO</t>
   </si>
   <si>
-    <t>PMP.090681.127234</t>
-  </si>
-  <si>
-    <t>PMP. 081274. 00987</t>
-  </si>
-  <si>
-    <t>PMP. 090473. 00912</t>
-  </si>
-  <si>
-    <t>PMP.040770.00890</t>
-  </si>
-  <si>
-    <t>PMP.17051987.30099</t>
-  </si>
-  <si>
-    <t>PMP. 160888. 125169</t>
-  </si>
-  <si>
-    <t>PRP.290593.46837</t>
-  </si>
-  <si>
-    <t>PRP.210595.128221</t>
-  </si>
-  <si>
-    <t>PRP. 281195. 39874</t>
-  </si>
-  <si>
-    <t>PRP.261287.45266</t>
-  </si>
-  <si>
-    <t>PRP.170384.128690</t>
-  </si>
-  <si>
-    <t>PRP.27071990.29611</t>
-  </si>
-  <si>
-    <t>PRP.230400.75621</t>
-  </si>
-  <si>
-    <t>PRP.100998.62399</t>
-  </si>
-  <si>
-    <t>PRP. 110489. 128220</t>
-  </si>
-  <si>
-    <t>PRP.310182.00732</t>
-  </si>
-  <si>
-    <t>PRP.070893.00695</t>
-  </si>
-  <si>
-    <t>PRP.090500.70413</t>
-  </si>
-  <si>
-    <t>PRP.170102.73669</t>
-  </si>
-  <si>
-    <t>PRP.230693.53313</t>
-  </si>
-  <si>
-    <t>PRP.110504.74227</t>
-  </si>
-  <si>
-    <t>PRP.220101.74153</t>
-  </si>
-  <si>
-    <t>PRP.220702.73675</t>
-  </si>
-  <si>
-    <t>PRP.29101990.32325</t>
-  </si>
-  <si>
-    <t>PRP.100491.128223</t>
-  </si>
-  <si>
-    <t>PRP. 070992. 40888</t>
-  </si>
-  <si>
-    <t>PRP.290396.45265</t>
-  </si>
-  <si>
-    <t>PRP.260695.122287</t>
-  </si>
-  <si>
-    <t>PRP.280396.41455</t>
-  </si>
-  <si>
-    <t>PRP.010997.74152</t>
-  </si>
-  <si>
-    <t>PRP.171191.00731</t>
-  </si>
-  <si>
-    <t>PRP.231202.73672</t>
-  </si>
-  <si>
-    <t>PRP.270584.00773</t>
-  </si>
-  <si>
-    <t>PRP.290990.128462</t>
-  </si>
-  <si>
-    <t>PRP.100789.39883</t>
-  </si>
-  <si>
-    <t>PRP.030302.72850</t>
-  </si>
-  <si>
-    <t>PRP.080402.72848</t>
-  </si>
-  <si>
-    <t>PRP. 060692.40889</t>
-  </si>
-  <si>
-    <t>PRP.150391.45071</t>
-  </si>
-  <si>
-    <t>PRP.270796.62691</t>
-  </si>
-  <si>
-    <t>PRP. 030990. 128214</t>
-  </si>
-  <si>
-    <t>PRP.290886.00779</t>
-  </si>
-  <si>
-    <t>PRP.261270.128269</t>
-  </si>
-  <si>
-    <t>PRP.101183.00778</t>
-  </si>
-  <si>
-    <t>PRP. 030394. 39882</t>
-  </si>
-  <si>
-    <t>PRP. 060397. 39879</t>
-  </si>
-  <si>
-    <t>PRP. 261292. 39881</t>
-  </si>
-  <si>
-    <t>PRP.100200.67473</t>
-  </si>
-  <si>
-    <t>PRP.180698.70414</t>
-  </si>
-  <si>
-    <t>PRP.240888.128245</t>
-  </si>
-  <si>
-    <t>PRP.190791.00776</t>
-  </si>
-  <si>
-    <t>PRP.120290.128460</t>
-  </si>
-  <si>
-    <t>PRP.240577.00780</t>
-  </si>
-  <si>
-    <t>PRP.260601.74154</t>
-  </si>
-  <si>
-    <t>PRP. 270492. 39876</t>
-  </si>
-  <si>
-    <t>PRP. 110392. 39877</t>
-  </si>
-  <si>
-    <t>PRP. 210888. 00781</t>
-  </si>
-  <si>
-    <t>PRP.280801.73671</t>
-  </si>
-  <si>
-    <t>PRP.261299.74151</t>
-  </si>
-  <si>
-    <t>PRP. 090189. 128267</t>
-  </si>
-  <si>
-    <t>PRP.270775.00701</t>
-  </si>
-  <si>
-    <t>PRP. 120880. 128213</t>
-  </si>
-  <si>
-    <t>PRP. 170892. 38996</t>
-  </si>
-  <si>
-    <t>PRP.28021989.33797</t>
-  </si>
-  <si>
-    <t>PRP.190387.41454</t>
-  </si>
-  <si>
-    <t>PRP.020998.74237</t>
-  </si>
-  <si>
-    <t>PRP. 051192.40885</t>
-  </si>
-  <si>
-    <t>PRP.230797.74702</t>
-  </si>
-  <si>
-    <t>PRP. 310187. 00699</t>
-  </si>
-  <si>
-    <t>PRP.080202.71444</t>
-  </si>
-  <si>
-    <t>PRP.091202.76820</t>
-  </si>
-  <si>
-    <t>PRP.030488.128222</t>
-  </si>
-  <si>
-    <t>PRP.011090.128506</t>
-  </si>
-  <si>
-    <t>PRP.171087.00741</t>
-  </si>
-  <si>
-    <t>PRP.310704.74156</t>
-  </si>
-  <si>
-    <t>PRP.080302.74701</t>
-  </si>
-  <si>
-    <t>PRP.121078.00742</t>
-  </si>
-  <si>
-    <t>PRP. 220493. 40887</t>
-  </si>
-  <si>
-    <t>PRP.020900.62692</t>
-  </si>
-  <si>
-    <t>PRP.301198.74791</t>
-  </si>
-  <si>
-    <t>PRP.110696.74157</t>
-  </si>
-  <si>
-    <t>PRP. 010697. 00739</t>
-  </si>
-  <si>
-    <t>PRP.170989.00784</t>
-  </si>
-  <si>
-    <t>PRP.310594.47459</t>
-  </si>
-  <si>
-    <t>PRP. 111195. 38781</t>
-  </si>
-  <si>
-    <t>PRP.140700.74703</t>
-  </si>
-  <si>
-    <t>PRP.190402.74155</t>
-  </si>
-  <si>
-    <t>PRP. 130393. 38995</t>
-  </si>
-  <si>
-    <t>PRP.071199.66246</t>
-  </si>
-  <si>
-    <t>PRP.250902.72849</t>
-  </si>
-  <si>
-    <t>PRP. 130190. 128244</t>
-  </si>
-  <si>
-    <t>PRP. 120493. 38780</t>
-  </si>
-  <si>
-    <t>PRP.190986.00744</t>
-  </si>
-  <si>
-    <t>PRP. 300987. 39473</t>
-  </si>
-  <si>
-    <t>PRP.231003.72846</t>
-  </si>
-  <si>
-    <t>PRP.200302.71443</t>
-  </si>
-  <si>
-    <t>PRP.230788.00785</t>
-  </si>
-  <si>
-    <t>PRP.120191.53311</t>
-  </si>
-  <si>
-    <t>PRP.140204.73670</t>
-  </si>
-  <si>
     <t>PRP.120198.72312</t>
-  </si>
-  <si>
-    <t>PMP.120677.01124</t>
-  </si>
-  <si>
-    <t>PMP.081274.00987</t>
-  </si>
-  <si>
-    <t>PMP.18061971.30714</t>
-  </si>
-  <si>
-    <t>PMP.160888.125169</t>
-  </si>
-  <si>
-    <t>PMP.030990.65326</t>
-  </si>
-  <si>
-    <t>PMP.090889.67647</t>
-  </si>
-  <si>
-    <t>PMP.130190.71596</t>
   </si>
 </sst>
 </file>
@@ -1119,9 +1215,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1130,8 +1223,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1435,30 +1531,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T119"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1480,7 +1575,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1489,19 +1584,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1510,7 +1605,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1522,10 +1617,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C2" s="2">
         <v>58201</v>
@@ -1536,13 +1631,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>50</v>
+      <c r="F2" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45901</v>
       </c>
       <c r="I2" s="2">
@@ -1551,34 +1646,31 @@
       <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>40269</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>29746</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>50222</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="Q2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" s="5">
         <v>47114</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="R2" s="6">
-        <v>47114</v>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C3" s="2">
         <v>46314</v>
@@ -1589,14 +1681,14 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>52</v>
+      <c r="F3" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
-        <v>46013</v>
+      <c r="H3" s="5">
+        <v>44481</v>
       </c>
       <c r="I3" s="2">
         <v>11</v>
@@ -1604,30 +1696,22 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>35490</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>28288</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>48761</v>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="R3" s="6">
-        <v>45979</v>
-      </c>
-      <c r="S3" s="3"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2">
         <v>43391</v>
@@ -1638,13 +1722,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>54</v>
+      <c r="F4" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45945</v>
       </c>
       <c r="I4" s="2">
@@ -1653,36 +1737,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35217</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>27371</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>47849</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45696</v>
-      </c>
-      <c r="P4" s="3"/>
       <c r="Q4" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="R4" s="6">
+        <v>91</v>
+      </c>
+      <c r="R4" s="5">
         <v>47324</v>
       </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2">
         <v>42098</v>
@@ -1693,13 +1772,13 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>56</v>
+      <c r="F5" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45870</v>
       </c>
       <c r="I5" s="2">
@@ -1708,35 +1787,22 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
-        <v>34346</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="K5" s="5">
+        <v>34669</v>
+      </c>
+      <c r="L5" s="5">
         <v>26763</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>47239</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45696</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="R5" s="6">
-        <v>45696</v>
-      </c>
-      <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2">
         <v>40393</v>
@@ -1747,13 +1813,13 @@
       <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>58</v>
+      <c r="F6" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>45839</v>
       </c>
       <c r="I6" s="2">
@@ -1762,35 +1828,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>33543</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>25753</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>46235</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6" s="5">
         <v>47114</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="R6" s="6">
-        <v>47114</v>
-      </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2">
         <v>42621</v>
@@ -1801,14 +1863,14 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>60</v>
+      <c r="F7" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
-        <v>46060</v>
+      <c r="H7" s="5">
+        <v>45839</v>
       </c>
       <c r="I7" s="2">
         <v>11</v>
@@ -1816,28 +1878,22 @@
       <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>34669</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>26102</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>46569</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="R7" s="6">
-        <v>45921</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2">
         <v>61971</v>
@@ -1848,13 +1904,13 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>62</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>45096</v>
       </c>
       <c r="I8" s="2">
@@ -1863,35 +1919,31 @@
       <c r="J8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>41153</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>31914</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>52383</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="O8" s="6">
-        <v>45825</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="R8" s="6">
+        <v>101</v>
+      </c>
+      <c r="R8" s="5">
         <v>47285</v>
       </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>62999</v>
@@ -1902,13 +1954,13 @@
       <c r="E9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>64</v>
+      <c r="F9" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>45550</v>
       </c>
       <c r="I9" s="2">
@@ -1917,35 +1969,31 @@
       <c r="J9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>41487</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>32371</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>52841</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O9" s="6">
-        <v>45605</v>
-      </c>
       <c r="Q9" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="R9" s="6">
+        <v>104</v>
+      </c>
+      <c r="R9" s="5">
         <v>47370</v>
       </c>
-      <c r="S9" s="3"/>
+      <c r="S9" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2">
         <v>57750</v>
@@ -1956,14 +2004,14 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>66</v>
+      <c r="F10" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+      <c r="H10" s="5">
+        <v>42491</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
@@ -1971,22 +2019,22 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>40163</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>32556</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>53022</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2">
         <v>69538</v>
@@ -1997,14 +2045,14 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>45</v>
+      <c r="F11" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+      <c r="H11" s="5">
+        <v>42767</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
@@ -2012,29 +2060,31 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L11" s="5">
         <v>34118</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>54575</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O11" s="6">
+        <v>108</v>
+      </c>
+      <c r="O11" s="5">
         <v>46595</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="P11" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
         <v>73798</v>
@@ -2045,14 +2095,14 @@
       <c r="E12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>45</v>
+      <c r="F12" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="6">
-        <v>44927</v>
+      <c r="H12" s="5">
+        <v>43891</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -2060,29 +2110,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>43780</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>34840</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>55305</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="O12" s="6">
+        <v>110</v>
+      </c>
+      <c r="O12" s="5">
         <v>47370</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="P12" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2">
         <v>70102</v>
@@ -2093,13 +2145,13 @@
       <c r="E13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>46</v>
+      <c r="F13" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>45597</v>
       </c>
       <c r="I13" s="2">
@@ -2108,29 +2160,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>42597</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>35031</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>55488</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O13" s="6">
+        <v>112</v>
+      </c>
+      <c r="O13" s="5">
         <v>46446</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>66890</v>
@@ -2141,13 +2195,13 @@
       <c r="E14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>46</v>
+      <c r="F14" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>45901</v>
       </c>
       <c r="I14" s="2">
@@ -2156,29 +2210,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>42226</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>32137</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>52597</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O14" s="6">
+        <v>114</v>
+      </c>
+      <c r="O14" s="5">
         <v>46550</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="P14" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2">
         <v>40840</v>
@@ -2189,13 +2245,13 @@
       <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>72</v>
+      <c r="F15" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="6">
+        <v>117</v>
+      </c>
+      <c r="H15" s="5">
         <v>45870</v>
       </c>
       <c r="I15" s="2">
@@ -2204,23 +2260,22 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
-        <v>33247</v>
-      </c>
-      <c r="L15" s="6">
+      <c r="K15" s="5">
+        <v>33482</v>
+      </c>
+      <c r="L15" s="5">
         <v>26069</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>46539</v>
       </c>
-      <c r="S15" s="3"/>
     </row>
     <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2">
         <v>62885</v>
@@ -2231,13 +2286,13 @@
       <c r="E16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>75</v>
+      <c r="F16" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="6">
+        <v>117</v>
+      </c>
+      <c r="H16" s="5">
         <v>45597</v>
       </c>
       <c r="I16" s="2">
@@ -2246,29 +2301,31 @@
       <c r="J16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>41456</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>30758</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>51227</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O16" s="6">
+        <v>120</v>
+      </c>
+      <c r="O16" s="5">
         <v>47370</v>
       </c>
-      <c r="S16" s="3"/>
+      <c r="P16" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C17" s="2">
         <v>57743</v>
@@ -2279,13 +2336,13 @@
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>77</v>
+      <c r="F17" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="6">
+        <v>117</v>
+      </c>
+      <c r="H17" s="5">
         <v>45884</v>
       </c>
       <c r="I17" s="2">
@@ -2294,29 +2351,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>40163</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>33081</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>53540</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O17" s="6">
+        <v>123</v>
+      </c>
+      <c r="O17" s="5">
         <v>47324</v>
       </c>
-      <c r="S17" s="3"/>
+      <c r="P17" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="C18" s="2">
         <v>75072</v>
@@ -2325,15 +2384,15 @@
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="6">
+        <v>117</v>
+      </c>
+      <c r="H18" s="5">
         <v>45627</v>
       </c>
       <c r="I18" s="2">
@@ -2342,22 +2401,22 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>44866</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>37588</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>58045</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C19" s="2">
         <v>75088</v>
@@ -2366,15 +2425,15 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="6">
+        <v>117</v>
+      </c>
+      <c r="H19" s="5">
         <v>45627</v>
       </c>
       <c r="I19" s="2">
@@ -2383,29 +2442,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>44866</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>36639</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>57101</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O19" s="6">
+        <v>127</v>
+      </c>
+      <c r="O19" s="5">
         <v>47370</v>
       </c>
-      <c r="S19" s="3"/>
+      <c r="P19" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="C20" s="2">
         <v>75196</v>
@@ -2414,15 +2475,15 @@
         <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>79</v>
+        <v>46</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="6">
+        <v>117</v>
+      </c>
+      <c r="H20" s="5">
         <v>45641</v>
       </c>
       <c r="I20" s="2">
@@ -2431,29 +2492,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>44866</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>36048</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>56523</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="O20" s="6">
+        <v>129</v>
+      </c>
+      <c r="O20" s="5">
         <v>46965</v>
       </c>
-      <c r="S20" s="3"/>
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="C21" s="2">
         <v>57724</v>
@@ -2464,13 +2527,13 @@
       <c r="E21" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>83</v>
+      <c r="F21" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="6">
+        <v>132</v>
+      </c>
+      <c r="H21" s="5">
         <v>45597</v>
       </c>
       <c r="I21" s="2">
@@ -2479,29 +2542,22 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>40163</v>
       </c>
-      <c r="L21" s="6">
-        <v>32816</v>
-      </c>
-      <c r="M21" s="6">
-        <v>53297</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O21" s="6">
-        <v>45747</v>
-      </c>
-      <c r="S21" s="3"/>
+      <c r="L21" s="5">
+        <v>32609</v>
+      </c>
+      <c r="M21" s="5">
+        <v>53083</v>
+      </c>
     </row>
     <row r="22" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="C22" s="2">
         <v>60266</v>
@@ -2512,13 +2568,13 @@
       <c r="E22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>86</v>
+      <c r="F22" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="6">
+        <v>132</v>
+      </c>
+      <c r="H22" s="5">
         <v>45597</v>
       </c>
       <c r="I22" s="2">
@@ -2527,29 +2583,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="K22" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L22" s="5">
         <v>29982</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>50437</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="O22" s="6">
+        <v>135</v>
+      </c>
+      <c r="O22" s="5">
         <v>46861</v>
       </c>
-      <c r="S22" s="3"/>
+      <c r="P22" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="23" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2">
         <v>61557</v>
@@ -2560,13 +2618,13 @@
       <c r="E23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>88</v>
+      <c r="F23" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="6">
+        <v>132</v>
+      </c>
+      <c r="H23" s="5">
         <v>45597</v>
       </c>
       <c r="I23" s="2">
@@ -2575,29 +2633,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L23" s="6">
-        <v>34158</v>
-      </c>
-      <c r="M23" s="6">
-        <v>54636</v>
+      <c r="K23" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L23" s="5">
+        <v>34188</v>
+      </c>
+      <c r="M23" s="5">
+        <v>54667</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O23" s="6">
+        <v>138</v>
+      </c>
+      <c r="O23" s="5">
         <v>47370</v>
       </c>
-      <c r="S23" s="3"/>
+      <c r="P23" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="C24" s="2">
         <v>75144</v>
@@ -2608,13 +2668,13 @@
       <c r="E24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>90</v>
+      <c r="F24" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="6">
+        <v>132</v>
+      </c>
+      <c r="H24" s="5">
         <v>45627</v>
       </c>
       <c r="I24" s="2">
@@ -2623,29 +2683,31 @@
       <c r="J24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>44866</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>36655</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>57132</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O24" s="6">
+        <v>141</v>
+      </c>
+      <c r="O24" s="5">
         <v>47232</v>
       </c>
-      <c r="S24" s="3"/>
+      <c r="P24" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="C25" s="2">
         <v>74969</v>
@@ -2656,13 +2718,13 @@
       <c r="E25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>90</v>
+      <c r="F25" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="6">
+        <v>132</v>
+      </c>
+      <c r="H25" s="5">
         <v>45901</v>
       </c>
       <c r="I25" s="2">
@@ -2671,28 +2733,31 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>44866</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>37273</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>57742</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O25" s="6">
+        <v>143</v>
+      </c>
+      <c r="O25" s="5">
         <v>47324</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="C26" s="2">
         <v>70099</v>
@@ -2703,13 +2768,13 @@
       <c r="E26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>93</v>
+      <c r="F26" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="6">
+        <v>132</v>
+      </c>
+      <c r="H26" s="5">
         <v>45627</v>
       </c>
       <c r="I26" s="2">
@@ -2718,29 +2783,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="5">
         <v>42597</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="5">
         <v>34143</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>54605</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O26" s="6">
+        <v>146</v>
+      </c>
+      <c r="O26" s="5">
         <v>46819</v>
       </c>
-      <c r="S26" s="3"/>
+      <c r="P26" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2">
         <v>75201</v>
@@ -2751,13 +2818,13 @@
       <c r="E27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>93</v>
+      <c r="F27" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="6">
+        <v>132</v>
+      </c>
+      <c r="H27" s="5">
         <v>45884</v>
       </c>
       <c r="I27" s="2">
@@ -2766,29 +2833,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>44866</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>38118</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>58593</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O27" s="6">
+        <v>148</v>
+      </c>
+      <c r="O27" s="5">
         <v>47324</v>
       </c>
-      <c r="S27" s="3"/>
+      <c r="P27" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C28" s="2">
         <v>75078</v>
@@ -2799,13 +2868,13 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>93</v>
+      <c r="F28" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H28" s="6">
+        <v>132</v>
+      </c>
+      <c r="H28" s="5">
         <v>45627</v>
       </c>
       <c r="I28" s="2">
@@ -2814,29 +2883,31 @@
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>44866</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>36913</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>57377</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O28" s="6">
+        <v>150</v>
+      </c>
+      <c r="O28" s="5">
         <v>47324</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="C29" s="2">
         <v>75086</v>
@@ -2847,13 +2918,13 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>93</v>
+      <c r="F29" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="6">
+        <v>132</v>
+      </c>
+      <c r="H29" s="5">
         <v>45627</v>
       </c>
       <c r="I29" s="2">
@@ -2862,23 +2933,22 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>44866</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>38190</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>58654</v>
       </c>
-      <c r="S29" s="3"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="C30" s="2">
         <v>74622</v>
@@ -2889,13 +2959,13 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>93</v>
+      <c r="F30" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="6">
+        <v>132</v>
+      </c>
+      <c r="H30" s="5">
         <v>45627</v>
       </c>
       <c r="I30" s="2">
@@ -2904,29 +2974,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>44866</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>37459</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>57923</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="O30" s="6">
+        <v>153</v>
+      </c>
+      <c r="O30" s="5">
         <v>47324</v>
       </c>
-      <c r="S30" s="3"/>
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2">
         <v>70161</v>
@@ -2937,14 +3009,14 @@
       <c r="E31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>99</v>
+      <c r="F31" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H31" s="6">
-        <v>46060</v>
+        <v>156</v>
+      </c>
+      <c r="H31" s="5">
+        <v>45627</v>
       </c>
       <c r="I31" s="2">
         <v>9</v>
@@ -2952,23 +3024,40 @@
       <c r="J31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>42611</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="5">
         <v>34077</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="5">
         <v>54544</v>
       </c>
-      <c r="S31" s="3"/>
+      <c r="N31" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O31" s="5">
+        <v>46663</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R31" s="5">
+        <v>47054</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="C32" s="2">
         <v>57786</v>
@@ -2979,13 +3068,13 @@
       <c r="E32" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>102</v>
+      <c r="F32" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" s="6">
+        <v>156</v>
+      </c>
+      <c r="H32" s="5">
         <v>45580</v>
       </c>
       <c r="I32" s="2">
@@ -2994,29 +3083,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>40163</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>33175</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>53632</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O32" s="6">
+        <v>161</v>
+      </c>
+      <c r="O32" s="5">
         <v>47370</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P32" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c r="C33" s="2">
         <v>57739</v>
@@ -3027,13 +3118,13 @@
       <c r="E33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>104</v>
+      <c r="F33" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" s="6">
+        <v>156</v>
+      </c>
+      <c r="H33" s="5">
         <v>45884</v>
       </c>
       <c r="I33" s="2">
@@ -3042,28 +3133,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>40163</v>
       </c>
-      <c r="L33" s="6">
-        <v>33515</v>
-      </c>
-      <c r="M33" s="6">
-        <v>53997</v>
+      <c r="L33" s="5">
+        <v>33338</v>
+      </c>
+      <c r="M33" s="5">
+        <v>53813</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O33" s="6">
+        <v>164</v>
+      </c>
+      <c r="O33" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P33" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2">
         <v>69738</v>
@@ -3074,14 +3168,14 @@
       <c r="E34" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>106</v>
+      <c r="F34" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="6">
-        <v>45119</v>
+        <v>156</v>
+      </c>
+      <c r="H34" s="5">
+        <v>45627</v>
       </c>
       <c r="I34" s="2">
         <v>5</v>
@@ -3089,29 +3183,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L34" s="6">
-        <v>33794</v>
-      </c>
-      <c r="M34" s="6">
-        <v>54271</v>
+      <c r="K34" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L34" s="5">
+        <v>33854</v>
+      </c>
+      <c r="M34" s="5">
+        <v>54332</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O34" s="6">
+        <v>167</v>
+      </c>
+      <c r="O34" s="5">
         <v>46433</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P34" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="C35" s="2">
         <v>45078</v>
@@ -3122,14 +3218,14 @@
       <c r="E35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>106</v>
+      <c r="F35" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="6">
-        <v>44927</v>
+        <v>156</v>
+      </c>
+      <c r="H35" s="5">
+        <v>45627</v>
       </c>
       <c r="I35" s="2">
         <v>5</v>
@@ -3137,23 +3233,22 @@
       <c r="J35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>35217</v>
       </c>
-      <c r="L35" s="6">
-        <v>25998</v>
-      </c>
-      <c r="M35" s="6">
+      <c r="L35" s="5">
+        <v>25999</v>
+      </c>
+      <c r="M35" s="5">
         <v>46478</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2">
         <v>66889</v>
@@ -3164,14 +3259,14 @@
       <c r="E36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>106</v>
+      <c r="F36" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H36" s="6">
-        <v>44927</v>
+        <v>156</v>
+      </c>
+      <c r="H36" s="5">
+        <v>45627</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -3179,29 +3274,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L36" s="6">
+      <c r="K36" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L36" s="5">
         <v>35153</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>55610</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O36" s="6">
+        <v>170</v>
+      </c>
+      <c r="O36" s="5">
         <v>46550</v>
       </c>
-      <c r="S36" s="3"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P36" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="C37" s="2">
         <v>72318</v>
@@ -3212,14 +3309,14 @@
       <c r="E37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>106</v>
+      <c r="F37" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H37" s="6">
-        <v>44927</v>
+        <v>156</v>
+      </c>
+      <c r="H37" s="5">
+        <v>45627</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -3227,29 +3324,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="K37" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L37" s="5">
         <v>34876</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>55335</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O37" s="6">
+        <v>172</v>
+      </c>
+      <c r="O37" s="5">
         <v>46861</v>
       </c>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="C38" s="2">
         <v>66893</v>
@@ -3260,13 +3359,13 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>106</v>
+      <c r="F38" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" s="6">
+        <v>156</v>
+      </c>
+      <c r="H38" s="5">
         <v>45627</v>
       </c>
       <c r="I38" s="2">
@@ -3275,29 +3374,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L38" s="6">
+      <c r="K38" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L38" s="5">
         <v>35152</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>55610</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="O38" s="6">
+        <v>174</v>
+      </c>
+      <c r="O38" s="5">
         <v>46476</v>
       </c>
-      <c r="S38" s="3"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="C39" s="2">
         <v>75118</v>
@@ -3308,13 +3409,13 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>106</v>
+      <c r="F39" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H39" s="6">
+        <v>156</v>
+      </c>
+      <c r="H39" s="5">
         <v>45627</v>
       </c>
       <c r="I39" s="2">
@@ -3323,28 +3424,31 @@
       <c r="J39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="5">
         <v>44866</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="5">
         <v>35674</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>56158</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="O39" s="6">
+        <v>176</v>
+      </c>
+      <c r="O39" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="C40" s="2">
         <v>57725</v>
@@ -3355,14 +3459,14 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>113</v>
+      <c r="F40" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H40" s="6">
-        <v>44927</v>
+        <v>156</v>
+      </c>
+      <c r="H40" s="5">
+        <v>45627</v>
       </c>
       <c r="I40" s="2">
         <v>5</v>
@@ -3370,29 +3474,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>40163</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>33559</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>54027</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O40" s="6">
+        <v>179</v>
+      </c>
+      <c r="O40" s="5">
         <v>47285</v>
       </c>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2">
         <v>75180</v>
@@ -3403,13 +3509,13 @@
       <c r="E41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>113</v>
+      <c r="F41" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H41" s="6">
+        <v>156</v>
+      </c>
+      <c r="H41" s="5">
         <v>45627</v>
       </c>
       <c r="I41" s="2">
@@ -3418,29 +3524,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>44866</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>37613</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>58076</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O41" s="6">
+        <v>181</v>
+      </c>
+      <c r="O41" s="5">
         <v>47324</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P41" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>31</v>
@@ -3448,26 +3556,22 @@
       <c r="E42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>115</v>
+      <c r="F42" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="6">
-        <v>45992</v>
+        <v>183</v>
       </c>
       <c r="I42" s="2">
         <v>8</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="C43" s="2">
         <v>60265</v>
@@ -3478,13 +3582,13 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>118</v>
+      <c r="F43" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" s="6">
+        <v>183</v>
+      </c>
+      <c r="H43" s="5">
         <v>45884</v>
       </c>
       <c r="I43" s="2">
@@ -3493,29 +3597,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L43" s="6">
+      <c r="K43" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L43" s="5">
         <v>30829</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>51288</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O43" s="6">
+        <v>186</v>
+      </c>
+      <c r="O43" s="5">
         <v>46861</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P43" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="C44" s="2">
         <v>57705</v>
@@ -3526,13 +3632,13 @@
       <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>120</v>
+      <c r="F44" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H44" s="6">
+        <v>183</v>
+      </c>
+      <c r="H44" s="5">
         <v>45597</v>
       </c>
       <c r="I44" s="2">
@@ -3541,29 +3647,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>40163</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>33145</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>53601</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="O44" s="6">
+        <v>189</v>
+      </c>
+      <c r="O44" s="5">
         <v>47285</v>
       </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P44" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="C45" s="2">
         <v>69549</v>
@@ -3574,14 +3682,14 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>122</v>
+      <c r="F45" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H45" s="6">
-        <v>45017</v>
+        <v>183</v>
+      </c>
+      <c r="H45" s="5">
+        <v>45627</v>
       </c>
       <c r="I45" s="2">
         <v>5</v>
@@ -3589,28 +3697,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L45" s="6">
-        <v>32788</v>
-      </c>
-      <c r="M45" s="6">
-        <v>53267</v>
+      <c r="K45" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L45" s="5">
+        <v>32699</v>
+      </c>
+      <c r="M45" s="5">
+        <v>53175</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O45" s="6">
+        <v>192</v>
+      </c>
+      <c r="O45" s="5">
         <v>46446</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="C46" s="2">
         <v>75183</v>
@@ -3621,13 +3732,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>122</v>
+      <c r="F46" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H46" s="6">
+        <v>183</v>
+      </c>
+      <c r="H46" s="5">
         <v>45627</v>
       </c>
       <c r="I46" s="2">
@@ -3636,29 +3747,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>44866</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>37318</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>57801</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O46" s="6">
+        <v>194</v>
+      </c>
+      <c r="O46" s="5">
         <v>47285</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>124</v>
+        <v>195</v>
       </c>
       <c r="C47" s="2">
         <v>75132</v>
@@ -3669,13 +3782,13 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>122</v>
+      <c r="F47" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H47" s="6">
+        <v>183</v>
+      </c>
+      <c r="H47" s="5">
         <v>45627</v>
       </c>
       <c r="I47" s="2">
@@ -3684,23 +3797,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>44866</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>37739</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>58196</v>
       </c>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N47" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="O47" s="5">
+        <v>47285</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="C48" s="2">
         <v>74657</v>
@@ -3711,13 +3832,13 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>122</v>
+      <c r="F48" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H48" s="6">
+        <v>183</v>
+      </c>
+      <c r="H48" s="5">
         <v>45627</v>
       </c>
       <c r="I48" s="2">
@@ -3726,29 +3847,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>44866</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>37354</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>57831</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="O48" s="6">
+        <v>198</v>
+      </c>
+      <c r="O48" s="5">
         <v>47285</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="P48" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="C49" s="2">
         <v>66995</v>
@@ -3759,14 +3882,14 @@
       <c r="E49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>127</v>
+      <c r="F49" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H49" s="6">
-        <v>44927</v>
+        <v>183</v>
+      </c>
+      <c r="H49" s="5">
+        <v>45627</v>
       </c>
       <c r="I49" s="2">
         <v>5</v>
@@ -3774,29 +3897,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L49" s="6">
+      <c r="K49" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L49" s="5">
         <v>33761</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>54240</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O49" s="6">
+        <v>201</v>
+      </c>
+      <c r="O49" s="5">
         <v>46433</v>
       </c>
-      <c r="S49" s="3"/>
+      <c r="P49" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>128</v>
+        <v>202</v>
       </c>
       <c r="C50" s="2">
         <v>70100</v>
@@ -3807,14 +3932,14 @@
       <c r="E50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>127</v>
+      <c r="F50" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H50" s="6">
-        <v>44927</v>
+        <v>183</v>
+      </c>
+      <c r="H50" s="5">
+        <v>45627</v>
       </c>
       <c r="I50" s="2">
         <v>5</v>
@@ -3822,29 +3947,31 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>42597</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>33312</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>53783</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O50" s="6">
+        <v>203</v>
+      </c>
+      <c r="O50" s="5">
         <v>46550</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="P50" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>129</v>
+        <v>204</v>
       </c>
       <c r="C51" s="2">
         <v>75139</v>
@@ -3855,14 +3982,14 @@
       <c r="E51" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>127</v>
+      <c r="F51" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H51" s="6">
-        <v>45366</v>
+        <v>183</v>
+      </c>
+      <c r="H51" s="5">
+        <v>45627</v>
       </c>
       <c r="I51" s="2">
         <v>5</v>
@@ -3870,29 +3997,31 @@
       <c r="J51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>44866</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>35273</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>55732</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O51" s="6">
+        <v>205</v>
+      </c>
+      <c r="O51" s="5">
         <v>46970</v>
       </c>
-      <c r="S51" s="3"/>
+      <c r="P51" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
       <c r="C52" s="2">
         <v>66894</v>
@@ -3903,13 +4032,13 @@
       <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>127</v>
+      <c r="F52" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H52" s="6">
+        <v>183</v>
+      </c>
+      <c r="H52" s="5">
         <v>45627</v>
       </c>
       <c r="I52" s="2">
@@ -3918,24 +4047,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L52" s="6">
-        <v>33302</v>
-      </c>
-      <c r="M52" s="6">
-        <v>53783</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
+      <c r="K52" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L52" s="5">
+        <v>33361</v>
+      </c>
+      <c r="M52" s="5">
+        <v>53844</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O52" s="5">
+        <v>46550</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="C53" s="2">
         <v>52916</v>
@@ -3946,13 +4082,13 @@
       <c r="E53" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>132</v>
+      <c r="F53" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H53" s="6">
+        <v>117</v>
+      </c>
+      <c r="H53" s="5">
         <v>45884</v>
       </c>
       <c r="I53" s="2">
@@ -3961,36 +4097,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L53" s="6">
-        <v>32941</v>
-      </c>
-      <c r="M53" s="6">
-        <v>53418</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O53" s="6">
-        <v>45747</v>
-      </c>
-      <c r="P53" s="3"/>
+      <c r="K53" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L53" s="5">
+        <v>33119</v>
+      </c>
+      <c r="M53" s="5">
+        <v>53601</v>
+      </c>
       <c r="Q53" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="R53" s="6">
+        <v>210</v>
+      </c>
+      <c r="R53" s="5">
         <v>47005</v>
       </c>
-      <c r="S53" s="3"/>
+      <c r="S53" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="54" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="C54" s="2">
         <v>57723</v>
@@ -4001,13 +4132,13 @@
       <c r="E54" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>134</v>
+      <c r="F54" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H54" s="6">
+        <v>213</v>
+      </c>
+      <c r="H54" s="5">
         <v>45580</v>
       </c>
       <c r="I54" s="2">
@@ -4016,30 +4147,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="5">
         <v>40163</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="5">
         <v>31653</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>52110</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="O54" s="6">
+        <v>214</v>
+      </c>
+      <c r="O54" s="5">
         <v>46861</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="P54" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="55" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="C55" s="2">
         <v>46622</v>
@@ -4050,13 +4182,13 @@
       <c r="E55" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>137</v>
+      <c r="F55" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H55" s="6">
+        <v>213</v>
+      </c>
+      <c r="H55" s="5">
         <v>45580</v>
       </c>
       <c r="I55" s="2">
@@ -4065,30 +4197,31 @@
       <c r="J55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K55" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L55" s="6">
+      <c r="K55" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L55" s="5">
         <v>25928</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>46388</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O55" s="6">
+        <v>217</v>
+      </c>
+      <c r="O55" s="5">
         <v>47285</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="C56" s="2">
         <v>60267</v>
@@ -4099,14 +4232,14 @@
       <c r="E56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>139</v>
+      <c r="F56" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H56" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H56" s="5">
+        <v>45627</v>
       </c>
       <c r="I56" s="2">
         <v>5</v>
@@ -4114,30 +4247,31 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L56" s="6">
-        <v>30600</v>
-      </c>
-      <c r="M56" s="6">
-        <v>51075</v>
+      <c r="K56" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L56" s="5">
+        <v>30630</v>
+      </c>
+      <c r="M56" s="5">
+        <v>51105</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O56" s="6">
+        <v>220</v>
+      </c>
+      <c r="O56" s="5">
         <v>47285</v>
       </c>
-      <c r="P56" s="3"/>
-      <c r="S56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="C57" s="2">
         <v>69526</v>
@@ -4148,14 +4282,14 @@
       <c r="E57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>139</v>
+      <c r="F57" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H57" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H57" s="5">
+        <v>45627</v>
       </c>
       <c r="I57" s="2">
         <v>5</v>
@@ -4163,30 +4297,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L57" s="6">
+      <c r="K57" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L57" s="5">
         <v>34396</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>54879</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O57" s="6">
+        <v>222</v>
+      </c>
+      <c r="O57" s="5">
         <v>46446</v>
       </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="P57" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="C58" s="2">
         <v>69543</v>
@@ -4197,14 +4332,14 @@
       <c r="E58" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>139</v>
+      <c r="F58" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H58" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H58" s="5">
+        <v>45627</v>
       </c>
       <c r="I58" s="2">
         <v>5</v>
@@ -4212,30 +4347,31 @@
       <c r="J58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L58" s="6">
-        <v>35584</v>
-      </c>
-      <c r="M58" s="6">
-        <v>56066</v>
+      <c r="K58" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L58" s="5">
+        <v>35495</v>
+      </c>
+      <c r="M58" s="5">
+        <v>55975</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="O58" s="6">
+        <v>224</v>
+      </c>
+      <c r="O58" s="5">
         <v>46446</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="P58" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2">
         <v>70104</v>
@@ -4246,14 +4382,14 @@
       <c r="E59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>143</v>
+      <c r="F59" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H59" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H59" s="5">
+        <v>45627</v>
       </c>
       <c r="I59" s="2">
         <v>5</v>
@@ -4261,30 +4397,31 @@
       <c r="J59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <v>42597</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>33964</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>54424</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O59" s="6">
+        <v>227</v>
+      </c>
+      <c r="O59" s="5">
         <v>46446</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="P59" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="C60" s="2">
         <v>74747</v>
@@ -4295,14 +4432,14 @@
       <c r="E60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>143</v>
+      <c r="F60" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H60" s="6">
-        <v>45505</v>
+        <v>213</v>
+      </c>
+      <c r="H60" s="5">
+        <v>45627</v>
       </c>
       <c r="I60" s="2">
         <v>5</v>
@@ -4310,30 +4447,31 @@
       <c r="J60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <v>44866</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>36566</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>57040</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O60" s="6">
+        <v>229</v>
+      </c>
+      <c r="O60" s="5">
         <v>47114</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="P60" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="C61" s="2">
         <v>75029</v>
@@ -4344,13 +4482,13 @@
       <c r="E61" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>143</v>
+      <c r="F61" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H61" s="6">
+        <v>213</v>
+      </c>
+      <c r="H61" s="5">
         <v>45627</v>
       </c>
       <c r="I61" s="2">
@@ -4359,30 +4497,31 @@
       <c r="J61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>44866</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="5">
         <v>35964</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="5">
         <v>56431</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O61" s="6">
+        <v>231</v>
+      </c>
+      <c r="O61" s="5">
         <v>47232</v>
       </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="C62" s="2">
         <v>75128</v>
@@ -4393,13 +4532,13 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>143</v>
+      <c r="F62" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H62" s="6">
+        <v>213</v>
+      </c>
+      <c r="H62" s="5">
         <v>45627</v>
       </c>
       <c r="I62" s="2">
@@ -4408,24 +4547,31 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <v>44866</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>37723</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>58196</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="N62" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="O62" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="C63" s="2">
         <v>52866</v>
@@ -4436,13 +4582,13 @@
       <c r="E63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>148</v>
+      <c r="F63" s="7" t="s">
+        <v>235</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H63" s="6">
+        <v>236</v>
+      </c>
+      <c r="H63" s="5">
         <v>45884</v>
       </c>
       <c r="I63" s="2">
@@ -4451,30 +4597,31 @@
       <c r="J63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K63" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L63" s="6">
+      <c r="K63" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L63" s="5">
         <v>32379</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>52841</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O63" s="6">
+        <v>237</v>
+      </c>
+      <c r="O63" s="5">
         <v>47370</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="64" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>150</v>
+        <v>238</v>
       </c>
       <c r="C64" s="2">
         <v>57744</v>
@@ -4485,13 +4632,13 @@
       <c r="E64" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>151</v>
+      <c r="F64" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H64" s="6">
+        <v>236</v>
+      </c>
+      <c r="H64" s="5">
         <v>45884</v>
       </c>
       <c r="I64" s="2">
@@ -4500,30 +4647,31 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="5">
         <v>40163</v>
       </c>
-      <c r="L64" s="6">
+      <c r="L64" s="5">
         <v>33438</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="5">
         <v>53905</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O64" s="6">
+        <v>240</v>
+      </c>
+      <c r="O64" s="5">
         <v>47285</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="P64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="C65" s="2">
         <v>57726</v>
@@ -4534,13 +4682,13 @@
       <c r="E65" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>153</v>
+      <c r="F65" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H65" s="6">
+        <v>236</v>
+      </c>
+      <c r="H65" s="5">
         <v>45597</v>
       </c>
       <c r="I65" s="2">
@@ -4549,30 +4697,22 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>40163</v>
       </c>
-      <c r="L65" s="6">
-        <v>33209</v>
-      </c>
-      <c r="M65" s="6">
-        <v>53693</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O65" s="6">
-        <v>45765</v>
-      </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="L65" s="5">
+        <v>32916</v>
+      </c>
+      <c r="M65" s="5">
+        <v>53387</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>154</v>
+        <v>243</v>
       </c>
       <c r="C66" s="2">
         <v>51667</v>
@@ -4583,14 +4723,14 @@
       <c r="E66" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>155</v>
+      <c r="F66" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H66" s="6">
-        <v>44927</v>
+        <v>236</v>
+      </c>
+      <c r="H66" s="5">
+        <v>45627</v>
       </c>
       <c r="I66" s="2">
         <v>5</v>
@@ -4598,30 +4738,31 @@
       <c r="J66" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K66" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L66" s="6">
+      <c r="K66" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L66" s="5">
         <v>28269</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <v>48731</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="O66" s="6">
+        <v>245</v>
+      </c>
+      <c r="O66" s="5">
         <v>47324</v>
       </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="P66" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="C67" s="2">
         <v>74664</v>
@@ -4632,14 +4773,14 @@
       <c r="E67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>155</v>
+      <c r="F67" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H67" s="6">
-        <v>45505</v>
+        <v>236</v>
+      </c>
+      <c r="H67" s="5">
+        <v>45627</v>
       </c>
       <c r="I67" s="2">
         <v>5</v>
@@ -4647,24 +4788,22 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>44866</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>37916</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>58380</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="C68" s="2">
         <v>75162</v>
@@ -4675,13 +4814,13 @@
       <c r="E68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>155</v>
+      <c r="F68" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H68" s="6">
+        <v>236</v>
+      </c>
+      <c r="H68" s="5">
         <v>45627</v>
       </c>
       <c r="I68" s="2">
@@ -4690,48 +4829,49 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <v>44866</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>37068</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="5">
         <v>57527</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="O68" s="6">
+        <v>248</v>
+      </c>
+      <c r="O68" s="5">
         <v>47324</v>
       </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C69" s="2">
         <v>66891</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>159</v>
+      <c r="F69" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H69" s="8">
-        <v>44927</v>
+        <v>236</v>
+      </c>
+      <c r="H69" s="5">
+        <v>45627</v>
       </c>
       <c r="I69" s="2">
         <v>5</v>
@@ -4739,48 +4879,49 @@
       <c r="J69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L69" s="6">
+      <c r="K69" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L69" s="5">
         <v>33721</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>54179</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="O69" s="6">
+        <v>251</v>
+      </c>
+      <c r="O69" s="5">
         <v>46446</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
+      <c r="P69" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="C70" s="2">
         <v>70101</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>159</v>
+      <c r="F70" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H70" s="8">
-        <v>44927</v>
+        <v>236</v>
+      </c>
+      <c r="H70" s="5">
+        <v>45627</v>
       </c>
       <c r="I70" s="2">
         <v>5</v>
@@ -4788,47 +4929,48 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <v>42597</v>
       </c>
-      <c r="L70" s="6">
-        <v>33911</v>
-      </c>
-      <c r="M70" s="6">
-        <v>54393</v>
+      <c r="L70" s="5">
+        <v>33674</v>
+      </c>
+      <c r="M70" s="5">
+        <v>54149</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="O70" s="6">
+        <v>253</v>
+      </c>
+      <c r="O70" s="5">
         <v>46446</v>
       </c>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
+      <c r="P70" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>161</v>
+        <v>254</v>
       </c>
       <c r="C71" s="2">
         <v>57773</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>159</v>
+      <c r="F71" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H71" s="6">
+        <v>236</v>
+      </c>
+      <c r="H71" s="5">
         <v>45627</v>
       </c>
       <c r="I71" s="2">
@@ -4837,47 +4979,39 @@
       <c r="J71" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="5">
         <v>40163</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="5">
         <v>32376</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>52841</v>
       </c>
-      <c r="N71" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O71" s="6">
-        <v>45766</v>
-      </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="C72" s="2">
         <v>75157</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>159</v>
+      <c r="F72" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H72" s="8">
+        <v>236</v>
+      </c>
+      <c r="H72" s="5">
         <v>45627</v>
       </c>
       <c r="I72" s="2">
@@ -4886,47 +5020,48 @@
       <c r="J72" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <v>44866</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>37131</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>57589</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="O72" s="6">
+        <v>256</v>
+      </c>
+      <c r="O72" s="5">
         <v>47324</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
+      <c r="P72" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="C73" s="2">
         <v>74991</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>159</v>
+      <c r="F73" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H73" s="8">
+        <v>236</v>
+      </c>
+      <c r="H73" s="5">
         <v>45627</v>
       </c>
       <c r="I73" s="2">
@@ -4935,47 +5070,48 @@
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>44866</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>36520</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="5">
         <v>56980</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="O73" s="6">
+        <v>258</v>
+      </c>
+      <c r="O73" s="5">
         <v>47324</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="P73" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="C74" s="2">
         <v>52882</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>165</v>
+      <c r="F74" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H74" s="6">
+        <v>261</v>
+      </c>
+      <c r="H74" s="5">
         <v>45992</v>
       </c>
       <c r="I74" s="2">
@@ -4984,53 +5120,48 @@
       <c r="J74" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L74" s="6">
-        <v>32759</v>
-      </c>
-      <c r="M74" s="6">
-        <v>53236</v>
-      </c>
-      <c r="N74" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="O74" s="6">
-        <v>45747</v>
-      </c>
-      <c r="P74" s="3"/>
+      <c r="K74" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L74" s="5">
+        <v>32729</v>
+      </c>
+      <c r="M74" s="5">
+        <v>53206</v>
+      </c>
       <c r="Q74" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="R74" s="6">
+        <v>262</v>
+      </c>
+      <c r="R74" s="5">
         <v>47114</v>
       </c>
-      <c r="S74" s="3"/>
+      <c r="S74" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="75" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>167</v>
+        <v>263</v>
       </c>
       <c r="C75" s="2">
         <v>51650</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>168</v>
+      <c r="F75" s="7" t="s">
+        <v>264</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H75" s="6">
+        <v>261</v>
+      </c>
+      <c r="H75" s="5">
         <v>45580</v>
       </c>
       <c r="I75" s="2">
@@ -5039,47 +5170,48 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L75" s="6">
+      <c r="K75" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L75" s="5">
         <v>27602</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>48061</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O75" s="6">
+        <v>265</v>
+      </c>
+      <c r="O75" s="5">
         <v>46574</v>
       </c>
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
+      <c r="P75" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="76" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>169</v>
+        <v>266</v>
       </c>
       <c r="C76" s="2">
         <v>57700</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>170</v>
+      <c r="F76" s="7" t="s">
+        <v>267</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H76" s="8">
+        <v>261</v>
+      </c>
+      <c r="H76" s="5">
         <v>45597</v>
       </c>
       <c r="I76" s="2">
@@ -5088,47 +5220,39 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="5">
         <v>40163</v>
       </c>
-      <c r="L76" s="6">
-        <v>29563</v>
-      </c>
-      <c r="M76" s="6">
-        <v>50041</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O76" s="6">
-        <v>45747</v>
-      </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="L76" s="5">
+        <v>29445</v>
+      </c>
+      <c r="M76" s="5">
+        <v>49919</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>171</v>
+        <v>268</v>
       </c>
       <c r="C77" s="2">
         <v>71771</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>172</v>
+      <c r="F77" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H77" s="8">
+        <v>261</v>
+      </c>
+      <c r="H77" s="5">
         <v>45627</v>
       </c>
       <c r="I77" s="2">
@@ -5137,47 +5261,48 @@
       <c r="J77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L77" s="6">
+      <c r="K77" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L77" s="5">
         <v>33833</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="5">
         <v>54302</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="O77" s="6">
+        <v>270</v>
+      </c>
+      <c r="O77" s="5">
         <v>46407</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
+      <c r="P77" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>173</v>
+        <v>271</v>
       </c>
       <c r="C78" s="2">
         <v>57550</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>172</v>
+      <c r="F78" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H78" s="8">
+        <v>261</v>
+      </c>
+      <c r="H78" s="5">
         <v>45627</v>
       </c>
       <c r="I78" s="2">
@@ -5186,47 +5311,48 @@
       <c r="J78" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="5">
         <v>40163</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="5">
         <v>32567</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="5">
         <v>53022</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O78" s="6">
+        <v>272</v>
+      </c>
+      <c r="O78" s="5">
         <v>46060</v>
       </c>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
+      <c r="P78" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="C79" s="2">
         <v>66993</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>172</v>
+      <c r="F79" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H79" s="8">
+        <v>261</v>
+      </c>
+      <c r="H79" s="5">
         <v>45627</v>
       </c>
       <c r="I79" s="2">
@@ -5235,47 +5361,48 @@
       <c r="J79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="6">
-        <v>42348</v>
-      </c>
-      <c r="L79" s="6">
+      <c r="K79" s="5">
+        <v>42289</v>
+      </c>
+      <c r="L79" s="5">
         <v>31855</v>
       </c>
-      <c r="M79" s="6">
+      <c r="M79" s="5">
         <v>52322</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="O79" s="6">
+        <v>274</v>
+      </c>
+      <c r="O79" s="5">
         <v>46476</v>
       </c>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
+      <c r="P79" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="C80" s="2">
         <v>75047</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>172</v>
+      <c r="F80" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H80" s="8">
+        <v>261</v>
+      </c>
+      <c r="H80" s="5">
         <v>45627</v>
       </c>
       <c r="I80" s="2">
@@ -5284,47 +5411,48 @@
       <c r="J80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="5">
         <v>44866</v>
       </c>
-      <c r="L80" s="6">
+      <c r="L80" s="5">
         <v>36040</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="5">
         <v>56523</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O80" s="6">
+        <v>276</v>
+      </c>
+      <c r="O80" s="5">
         <v>47324</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P80" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="C81" s="2">
         <v>69009</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>177</v>
+      <c r="F81" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H81" s="8">
+        <v>261</v>
+      </c>
+      <c r="H81" s="5">
         <v>45627</v>
       </c>
       <c r="I81" s="2">
@@ -5333,47 +5461,48 @@
       <c r="J81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L81" s="6">
-        <v>33735</v>
-      </c>
-      <c r="M81" s="6">
-        <v>54210</v>
+      <c r="K81" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L81" s="5">
+        <v>33913</v>
+      </c>
+      <c r="M81" s="5">
+        <v>54393</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O81" s="6">
+        <v>279</v>
+      </c>
+      <c r="O81" s="5">
         <v>46433</v>
       </c>
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P81" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>178</v>
+        <v>280</v>
       </c>
       <c r="C82" s="2">
         <v>75020</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>177</v>
+      <c r="F82" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H82" s="8">
+        <v>261</v>
+      </c>
+      <c r="H82" s="5">
         <v>45641</v>
       </c>
       <c r="I82" s="2">
@@ -5382,47 +5511,48 @@
       <c r="J82" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K82" s="6">
+      <c r="K82" s="5">
         <v>44866</v>
       </c>
-      <c r="L82" s="6">
+      <c r="L82" s="5">
         <v>35634</v>
       </c>
-      <c r="M82" s="6">
+      <c r="M82" s="5">
         <v>56097</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O82" s="6">
+        <v>281</v>
+      </c>
+      <c r="O82" s="5">
         <v>47370</v>
       </c>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P82" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="C83" s="2">
         <v>57735</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>177</v>
+      <c r="F83" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H83" s="8">
+        <v>261</v>
+      </c>
+      <c r="H83" s="5">
         <v>45627</v>
       </c>
       <c r="I83" s="2">
@@ -5431,47 +5561,39 @@
       <c r="J83" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="5">
         <v>40163</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="5">
         <v>31808</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="5">
         <v>52263</v>
       </c>
-      <c r="N83" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O83" s="6">
-        <v>45747</v>
-      </c>
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>180</v>
+        <v>283</v>
       </c>
       <c r="C84" s="2">
         <v>74699</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>177</v>
+      <c r="F84" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H84" s="6">
+        <v>261</v>
+      </c>
+      <c r="H84" s="5">
         <v>45627</v>
       </c>
       <c r="I84" s="2">
@@ -5480,47 +5602,48 @@
       <c r="J84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>44866</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>37295</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="5">
         <v>57770</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O84" s="6">
+        <v>284</v>
+      </c>
+      <c r="O84" s="5">
         <v>47265</v>
       </c>
-      <c r="P84" s="3"/>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P84" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="C85" s="2">
         <v>75156</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>177</v>
+      <c r="F85" s="7" t="s">
+        <v>278</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H85" s="6">
+        <v>261</v>
+      </c>
+      <c r="H85" s="5">
         <v>45641</v>
       </c>
       <c r="I85" s="2">
@@ -5529,75 +5652,71 @@
       <c r="J85" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K85" s="6">
+      <c r="K85" s="5">
         <v>44866</v>
       </c>
-      <c r="L85" s="6">
+      <c r="L85" s="5">
         <v>37599</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="5">
         <v>58076</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O85" s="6">
+        <v>286</v>
+      </c>
+      <c r="O85" s="5">
         <v>47418</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P85" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>182</v>
+      <c r="F86" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H86" s="6">
-        <v>46060</v>
+        <v>288</v>
       </c>
       <c r="I86" s="2">
         <v>8</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="87" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>184</v>
+        <v>289</v>
       </c>
       <c r="C87" s="2">
         <v>57311</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>185</v>
+      <c r="F87" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H87" s="8">
+        <v>288</v>
+      </c>
+      <c r="H87" s="5">
         <v>45580</v>
       </c>
       <c r="I87" s="2">
@@ -5606,47 +5725,48 @@
       <c r="J87" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="5">
         <v>40163</v>
       </c>
-      <c r="L87" s="6">
-        <v>32206</v>
-      </c>
-      <c r="M87" s="6">
-        <v>52688</v>
+      <c r="L87" s="5">
+        <v>32236</v>
+      </c>
+      <c r="M87" s="5">
+        <v>52718</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O87" s="6">
+        <v>291</v>
+      </c>
+      <c r="O87" s="5">
         <v>47324</v>
       </c>
-      <c r="P87" s="3"/>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P87" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="C88" s="2">
         <v>57819</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>187</v>
+      <c r="F88" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H88" s="8">
+        <v>288</v>
+      </c>
+      <c r="H88" s="5">
         <v>45884</v>
       </c>
       <c r="I88" s="2">
@@ -5655,47 +5775,48 @@
       <c r="J88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="5">
         <v>40163</v>
       </c>
-      <c r="L88" s="6">
-        <v>32883</v>
-      </c>
-      <c r="M88" s="6">
-        <v>53359</v>
+      <c r="L88" s="5">
+        <v>33147</v>
+      </c>
+      <c r="M88" s="5">
+        <v>53632</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="O88" s="6">
+        <v>294</v>
+      </c>
+      <c r="O88" s="5">
         <v>47370</v>
       </c>
-      <c r="P88" s="3"/>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P88" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>188</v>
+        <v>295</v>
       </c>
       <c r="C89" s="2">
         <v>57303</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>189</v>
+      <c r="F89" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H89" s="8">
+        <v>288</v>
+      </c>
+      <c r="H89" s="5">
         <v>45627</v>
       </c>
       <c r="I89" s="2">
@@ -5704,47 +5825,48 @@
       <c r="J89" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="5">
         <v>40163</v>
       </c>
-      <c r="L89" s="6">
+      <c r="L89" s="5">
         <v>32067</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="5">
         <v>52536</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="O89" s="6">
+        <v>297</v>
+      </c>
+      <c r="O89" s="5">
         <v>47285</v>
       </c>
-      <c r="P89" s="3"/>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P89" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="C90" s="2">
         <v>45080</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>189</v>
+      <c r="F90" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H90" s="6">
+        <v>288</v>
+      </c>
+      <c r="H90" s="5">
         <v>45627</v>
       </c>
       <c r="I90" s="2">
@@ -5753,41 +5875,39 @@
       <c r="J90" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="5">
         <v>35217</v>
       </c>
-      <c r="L90" s="6">
+      <c r="L90" s="5">
         <v>26032</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="5">
         <v>46508</v>
       </c>
-      <c r="P90" s="3"/>
-      <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>191</v>
+        <v>299</v>
       </c>
       <c r="C91" s="2">
         <v>75121</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>189</v>
+      <c r="F91" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H91" s="8">
+        <v>288</v>
+      </c>
+      <c r="H91" s="5">
         <v>45627</v>
       </c>
       <c r="I91" s="2">
@@ -5796,47 +5916,48 @@
       <c r="J91" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="5">
         <v>44866</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="5">
         <v>38199</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="5">
         <v>58654</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O91" s="6">
+        <v>300</v>
+      </c>
+      <c r="O91" s="5">
         <v>47324</v>
       </c>
-      <c r="P91" s="3"/>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P91" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>192</v>
+        <v>301</v>
       </c>
       <c r="C92" s="2">
         <v>76955</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>189</v>
+      <c r="F92" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H92" s="6">
+        <v>288</v>
+      </c>
+      <c r="H92" s="5">
         <v>45809</v>
       </c>
       <c r="I92" s="2">
@@ -5845,47 +5966,48 @@
       <c r="J92" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K92" s="6">
+      <c r="K92" s="5">
         <v>45289</v>
       </c>
-      <c r="L92" s="6">
+      <c r="L92" s="5">
         <v>37323</v>
       </c>
-      <c r="M92" s="6">
+      <c r="M92" s="5">
         <v>57801</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O92" s="6">
+        <v>302</v>
+      </c>
+      <c r="O92" s="5">
         <v>47370</v>
       </c>
-      <c r="P92" s="3"/>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P92" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="C93" s="2">
         <v>72404</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>194</v>
+      <c r="F93" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H93" s="6">
+        <v>288</v>
+      </c>
+      <c r="H93" s="5">
         <v>45627</v>
       </c>
       <c r="I93" s="2">
@@ -5894,39 +6016,48 @@
       <c r="J93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K93" s="6">
-        <v>43106</v>
-      </c>
-      <c r="L93" s="6">
+      <c r="K93" s="5">
+        <v>43252</v>
+      </c>
+      <c r="L93" s="5">
         <v>35848</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="5">
         <v>56309</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N93" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="O93" s="5">
+        <v>46819</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>195</v>
+        <v>306</v>
       </c>
       <c r="C94" s="2">
         <v>60268</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>194</v>
+      <c r="F94" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H94" s="6">
+        <v>288</v>
+      </c>
+      <c r="H94" s="5">
         <v>45627</v>
       </c>
       <c r="I94" s="2">
@@ -5935,45 +6066,48 @@
       <c r="J94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L94" s="6">
-        <v>28834</v>
-      </c>
-      <c r="M94" s="6">
-        <v>49310</v>
+      <c r="K94" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L94" s="5">
+        <v>28775</v>
+      </c>
+      <c r="M94" s="5">
+        <v>49249</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="O94" s="6">
+        <v>307</v>
+      </c>
+      <c r="O94" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P94" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="C95" s="2">
         <v>71780</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>194</v>
+      <c r="F95" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H95" s="6">
+        <v>288</v>
+      </c>
+      <c r="H95" s="5">
         <v>45627</v>
       </c>
       <c r="I95" s="2">
@@ -5982,45 +6116,48 @@
       <c r="J95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K95" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L95" s="6">
+      <c r="K95" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L95" s="5">
         <v>34081</v>
       </c>
-      <c r="M95" s="6">
+      <c r="M95" s="5">
         <v>54544</v>
       </c>
       <c r="N95" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O95" s="5">
+        <v>46433</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A96" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="O95" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A96" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="C96" s="2">
         <v>75009</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>194</v>
+      <c r="F96" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H96" s="6">
+        <v>288</v>
+      </c>
+      <c r="H96" s="5">
         <v>45627</v>
       </c>
       <c r="I96" s="2">
@@ -6029,45 +6166,48 @@
       <c r="J96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="6">
+      <c r="K96" s="5">
         <v>44866</v>
       </c>
-      <c r="L96" s="6">
+      <c r="L96" s="5">
         <v>36771</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="5">
         <v>57254</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="O96" s="6">
+      <c r="O96" s="5">
         <v>46970</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>198</v>
+        <v>312</v>
       </c>
       <c r="C97" s="2">
         <v>74885</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>194</v>
+      <c r="F97" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H97" s="6">
+        <v>288</v>
+      </c>
+      <c r="H97" s="5">
         <v>45627</v>
       </c>
       <c r="I97" s="2">
@@ -6076,45 +6216,48 @@
       <c r="J97" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K97" s="5">
         <v>44866</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L97" s="5">
         <v>36129</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="5">
         <v>56584</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O97" s="6">
+        <v>313</v>
+      </c>
+      <c r="O97" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>199</v>
+        <v>314</v>
       </c>
       <c r="C98" s="2">
         <v>74990</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>194</v>
+      <c r="F98" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H98" s="6">
+        <v>288</v>
+      </c>
+      <c r="H98" s="5">
         <v>45627</v>
       </c>
       <c r="I98" s="2">
@@ -6123,45 +6266,48 @@
       <c r="J98" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98" s="5">
         <v>44866</v>
       </c>
-      <c r="L98" s="6">
+      <c r="L98" s="5">
         <v>35227</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="5">
         <v>55701</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="O98" s="6">
+        <v>315</v>
+      </c>
+      <c r="O98" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="C99" s="2">
         <v>44862</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>201</v>
+      <c r="F99" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H99" s="6">
+        <v>318</v>
+      </c>
+      <c r="H99" s="5">
         <v>45580</v>
       </c>
       <c r="I99" s="2">
@@ -6170,39 +6316,48 @@
       <c r="J99" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K99" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L99" s="6">
+      <c r="K99" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L99" s="5">
         <v>26723</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="5">
         <v>47178</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="Q99" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="R99" s="5">
+        <v>47285</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>203</v>
+        <v>320</v>
       </c>
       <c r="C100" s="2">
         <v>57785</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>204</v>
+      <c r="F100" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H100" s="6">
+        <v>318</v>
+      </c>
+      <c r="H100" s="5">
         <v>45884</v>
       </c>
       <c r="I100" s="2">
@@ -6211,45 +6366,39 @@
       <c r="J100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="5">
         <v>40163</v>
       </c>
-      <c r="L100" s="6">
-        <v>31783</v>
-      </c>
-      <c r="M100" s="6">
-        <v>52263</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="O100" s="6">
-        <v>45810</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="L100" s="5">
+        <v>31929</v>
+      </c>
+      <c r="M100" s="5">
+        <v>52413</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>205</v>
+        <v>322</v>
       </c>
       <c r="C101" s="2">
         <v>57575</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>206</v>
+      <c r="F101" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H101" s="6">
+        <v>318</v>
+      </c>
+      <c r="H101" s="5">
         <v>45580</v>
       </c>
       <c r="I101" s="2">
@@ -6258,46 +6407,49 @@
       <c r="J101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K101" s="6">
+      <c r="K101" s="5">
         <v>40163</v>
       </c>
-      <c r="L101" s="6">
+      <c r="L101" s="5">
         <v>32768</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="5">
         <v>53236</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="O101" s="6">
+        <v>324</v>
+      </c>
+      <c r="O101" s="5">
         <v>46861</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P101" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>207</v>
+        <v>325</v>
       </c>
       <c r="C102" s="2">
         <v>66895</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>208</v>
+      <c r="F102" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H102" s="6">
-        <v>45264</v>
+        <v>318</v>
+      </c>
+      <c r="H102" s="5">
+        <v>45627</v>
       </c>
       <c r="I102" s="2">
         <v>5</v>
@@ -6305,45 +6457,48 @@
       <c r="J102" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K102" s="6">
-        <v>42285</v>
-      </c>
-      <c r="L102" s="6">
+      <c r="K102" s="5">
+        <v>42226</v>
+      </c>
+      <c r="L102" s="5">
         <v>34485</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="5">
         <v>54940</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O102" s="6">
+        <v>327</v>
+      </c>
+      <c r="O102" s="5">
         <v>46610</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="C103" s="2">
         <v>71820</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>208</v>
+      <c r="F103" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H103" s="6">
+        <v>318</v>
+      </c>
+      <c r="H103" s="5">
         <v>45627</v>
       </c>
       <c r="I103" s="2">
@@ -6352,45 +6507,48 @@
       <c r="J103" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K103" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L103" s="6">
+      <c r="K103" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L103" s="5">
         <v>35014</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="5">
         <v>55488</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="O103" s="6">
+        <v>329</v>
+      </c>
+      <c r="O103" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P103" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="C104" s="2">
         <v>75032</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>208</v>
+      <c r="F104" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H104" s="6">
+        <v>318</v>
+      </c>
+      <c r="H104" s="5">
         <v>45627</v>
       </c>
       <c r="I104" s="2">
@@ -6399,45 +6557,48 @@
       <c r="J104" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K104" s="6">
+      <c r="K104" s="5">
         <v>44866</v>
       </c>
-      <c r="L104" s="6">
+      <c r="L104" s="5">
         <v>36721</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="5">
         <v>57193</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="O104" s="6">
+        <v>331</v>
+      </c>
+      <c r="O104" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>211</v>
+        <v>332</v>
       </c>
       <c r="C105" s="2">
         <v>75089</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>208</v>
+      <c r="F105" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H105" s="6">
+        <v>318</v>
+      </c>
+      <c r="H105" s="5">
         <v>45884</v>
       </c>
       <c r="I105" s="2">
@@ -6446,46 +6607,49 @@
       <c r="J105" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K105" s="6">
+      <c r="K105" s="5">
         <v>44866</v>
       </c>
-      <c r="L105" s="6">
+      <c r="L105" s="5">
         <v>37365</v>
       </c>
-      <c r="M105" s="6">
+      <c r="M105" s="5">
         <v>57831</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O105" s="6">
+        <v>333</v>
+      </c>
+      <c r="O105" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P105" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>212</v>
+        <v>334</v>
       </c>
       <c r="C106" s="2">
         <v>71772</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>213</v>
+      <c r="F106" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H106" s="6">
-        <v>44927</v>
+        <v>318</v>
+      </c>
+      <c r="H106" s="5">
+        <v>45627</v>
       </c>
       <c r="I106" s="2">
         <v>5</v>
@@ -6493,40 +6657,49 @@
       <c r="J106" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K106" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L106" s="6">
-        <v>33971</v>
-      </c>
-      <c r="M106" s="6">
-        <v>54455</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="K106" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L106" s="5">
+        <v>34001</v>
+      </c>
+      <c r="M106" s="5">
+        <v>54483</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="O106" s="5">
+        <v>46819</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="C107" s="2">
         <v>71816</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>213</v>
+      <c r="F107" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H107" s="6">
-        <v>44927</v>
+        <v>318</v>
+      </c>
+      <c r="H107" s="5">
+        <v>45627</v>
       </c>
       <c r="I107" s="2">
         <v>5</v>
@@ -6534,46 +6707,49 @@
       <c r="J107" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K107" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L107" s="6">
+      <c r="K107" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L107" s="5">
         <v>34041</v>
       </c>
-      <c r="M107" s="6">
+      <c r="M107" s="5">
         <v>54514</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="O107" s="6">
+        <v>338</v>
+      </c>
+      <c r="O107" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P107" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>215</v>
+        <v>339</v>
       </c>
       <c r="C108" s="2">
         <v>74665</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F108" s="4" t="s">
-        <v>213</v>
+      <c r="F108" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H108" s="6">
-        <v>45505</v>
+        <v>318</v>
+      </c>
+      <c r="H108" s="5">
+        <v>45627</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
@@ -6581,45 +6757,48 @@
       <c r="J108" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K108" s="6">
+      <c r="K108" s="5">
         <v>44866</v>
       </c>
-      <c r="L108" s="6">
+      <c r="L108" s="5">
         <v>36471</v>
       </c>
-      <c r="M108" s="6">
+      <c r="M108" s="5">
         <v>56949</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O108" s="6">
+        <v>340</v>
+      </c>
+      <c r="O108" s="5">
         <v>47054</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P108" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="C109" s="2">
         <v>75147</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F109" s="4" t="s">
-        <v>213</v>
+      <c r="F109" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H109" s="6">
+        <v>318</v>
+      </c>
+      <c r="H109" s="5">
         <v>45641</v>
       </c>
       <c r="I109" s="2">
@@ -6628,45 +6807,48 @@
       <c r="J109" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K109" s="6">
+      <c r="K109" s="5">
         <v>44866</v>
       </c>
-      <c r="L109" s="6">
+      <c r="L109" s="5">
         <v>37524</v>
       </c>
-      <c r="M109" s="6">
+      <c r="M109" s="5">
         <v>57984</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O109" s="6">
+        <v>342</v>
+      </c>
+      <c r="O109" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P109" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>217</v>
+        <v>343</v>
       </c>
       <c r="C110" s="2">
         <v>57637</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F110" s="4" t="s">
-        <v>218</v>
+      <c r="F110" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H110" s="6">
+        <v>345</v>
+      </c>
+      <c r="H110" s="5">
         <v>45884</v>
       </c>
       <c r="I110" s="2">
@@ -6675,51 +6857,48 @@
       <c r="J110" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K110" s="6">
+      <c r="K110" s="5">
         <v>40163</v>
       </c>
-      <c r="L110" s="6">
+      <c r="L110" s="5">
         <v>32886</v>
       </c>
-      <c r="M110" s="6">
+      <c r="M110" s="5">
         <v>53359</v>
       </c>
-      <c r="N110" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="O110" s="6">
-        <v>45747</v>
-      </c>
       <c r="Q110" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R110" s="6">
+        <v>346</v>
+      </c>
+      <c r="R110" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S110" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>220</v>
+        <v>347</v>
       </c>
       <c r="C111" s="2">
         <v>70103</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>221</v>
+      <c r="F111" s="7" t="s">
+        <v>348</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H111" s="6">
+        <v>345</v>
+      </c>
+      <c r="H111" s="5">
         <v>45884</v>
       </c>
       <c r="I111" s="2">
@@ -6728,45 +6907,48 @@
       <c r="J111" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K111" s="6">
+      <c r="K111" s="5">
         <v>42597</v>
       </c>
-      <c r="L111" s="6">
-        <v>34307</v>
-      </c>
-      <c r="M111" s="6">
-        <v>54789</v>
+      <c r="L111" s="5">
+        <v>34071</v>
+      </c>
+      <c r="M111" s="5">
+        <v>54544</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O111" s="6">
+        <v>349</v>
+      </c>
+      <c r="O111" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P111" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>222</v>
+        <v>350</v>
       </c>
       <c r="C112" s="2">
         <v>57546</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F112" s="4" t="s">
-        <v>223</v>
+      <c r="F112" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H112" s="6">
+        <v>345</v>
+      </c>
+      <c r="H112" s="5">
         <v>45597</v>
       </c>
       <c r="I112" s="2">
@@ -6775,45 +6957,48 @@
       <c r="J112" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K112" s="6">
+      <c r="K112" s="5">
         <v>40163</v>
       </c>
-      <c r="L112" s="6">
+      <c r="L112" s="5">
         <v>31674</v>
       </c>
-      <c r="M112" s="6">
+      <c r="M112" s="5">
         <v>52140</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O112" s="6">
+        <v>352</v>
+      </c>
+      <c r="O112" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P112" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="C113" s="2">
         <v>67440</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>225</v>
+      <c r="F113" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H113" s="6">
+        <v>345</v>
+      </c>
+      <c r="H113" s="5">
         <v>45627</v>
       </c>
       <c r="I113" s="2">
@@ -6822,45 +7007,48 @@
       <c r="J113" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K113" s="6">
+      <c r="K113" s="5">
         <v>42248</v>
       </c>
-      <c r="L113" s="6">
+      <c r="L113" s="5">
         <v>32050</v>
       </c>
-      <c r="M113" s="6">
+      <c r="M113" s="5">
         <v>52505</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="O113" s="6">
+        <v>355</v>
+      </c>
+      <c r="O113" s="5">
         <v>46446</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P113" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>226</v>
+        <v>356</v>
       </c>
       <c r="C114" s="2">
         <v>74580</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F114" s="4" t="s">
-        <v>225</v>
+      <c r="F114" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H114" s="6">
+        <v>345</v>
+      </c>
+      <c r="H114" s="5">
         <v>45627</v>
       </c>
       <c r="I114" s="2">
@@ -6869,45 +7057,48 @@
       <c r="J114" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K114" s="6">
+      <c r="K114" s="5">
         <v>44866</v>
       </c>
-      <c r="L114" s="6">
+      <c r="L114" s="5">
         <v>37917</v>
       </c>
-      <c r="M114" s="6">
+      <c r="M114" s="5">
         <v>58380</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="O114" s="6">
+        <v>357</v>
+      </c>
+      <c r="O114" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P114" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="C115" s="2">
         <v>74583</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F115" s="4" t="s">
-        <v>225</v>
+      <c r="F115" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H115" s="6">
+        <v>345</v>
+      </c>
+      <c r="H115" s="5">
         <v>45627</v>
       </c>
       <c r="I115" s="2">
@@ -6916,45 +7107,48 @@
       <c r="J115" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K115" s="6">
+      <c r="K115" s="5">
         <v>44866</v>
       </c>
-      <c r="L115" s="6">
+      <c r="L115" s="5">
         <v>37335</v>
       </c>
-      <c r="M115" s="6">
+      <c r="M115" s="5">
         <v>57801</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="O115" s="6">
+        <v>359</v>
+      </c>
+      <c r="O115" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P115" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>228</v>
+        <v>360</v>
       </c>
       <c r="C116" s="2">
         <v>57354</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F116" s="4" t="s">
-        <v>229</v>
+      <c r="F116" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H116" s="6">
+        <v>345</v>
+      </c>
+      <c r="H116" s="5">
         <v>45627</v>
       </c>
       <c r="I116" s="2">
@@ -6963,45 +7157,48 @@
       <c r="J116" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K116" s="6">
+      <c r="K116" s="5">
         <v>40163</v>
       </c>
-      <c r="L116" s="6">
+      <c r="L116" s="5">
         <v>32347</v>
       </c>
-      <c r="M116" s="6">
+      <c r="M116" s="5">
         <v>52810</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="O116" s="6">
+        <v>362</v>
+      </c>
+      <c r="O116" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P116" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>230</v>
+        <v>363</v>
       </c>
       <c r="C117" s="2">
         <v>57630</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>229</v>
+      <c r="F117" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H117" s="6">
+        <v>345</v>
+      </c>
+      <c r="H117" s="5">
         <v>45627</v>
       </c>
       <c r="I117" s="2">
@@ -7010,45 +7207,48 @@
       <c r="J117" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K117" s="6">
+      <c r="K117" s="5">
         <v>40163</v>
       </c>
-      <c r="L117" s="6">
-        <v>33573</v>
-      </c>
-      <c r="M117" s="6">
-        <v>54058</v>
+      <c r="L117" s="5">
+        <v>33250</v>
+      </c>
+      <c r="M117" s="5">
+        <v>53724</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="O117" s="6">
+        <v>364</v>
+      </c>
+      <c r="O117" s="5">
         <v>46819</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P117" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="C118" s="2">
         <v>75166</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F118" s="4" t="s">
-        <v>229</v>
+      <c r="F118" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H118" s="6">
+        <v>345</v>
+      </c>
+      <c r="H118" s="5">
         <v>45627</v>
       </c>
       <c r="I118" s="2">
@@ -7057,45 +7257,48 @@
       <c r="J118" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K118" s="6">
+      <c r="K118" s="5">
         <v>44866</v>
       </c>
-      <c r="L118" s="6">
+      <c r="L118" s="5">
         <v>38031</v>
       </c>
-      <c r="M118" s="6">
+      <c r="M118" s="5">
         <v>58501</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="O118" s="6">
+        <v>366</v>
+      </c>
+      <c r="O118" s="5">
         <v>47324</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P118" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>232</v>
+        <v>367</v>
       </c>
       <c r="C119" s="2">
         <v>75006</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F119" s="4" t="s">
-        <v>229</v>
+      <c r="F119" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H119" s="6">
+        <v>345</v>
+      </c>
+      <c r="H119" s="5">
         <v>45641</v>
       </c>
       <c r="I119" s="2">
@@ -7104,46 +7307,148 @@
       <c r="J119" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K119" s="6">
+      <c r="K119" s="5">
         <v>44866</v>
       </c>
-      <c r="L119" s="6">
+      <c r="L119" s="5">
         <v>35807</v>
       </c>
-      <c r="M119" s="6">
+      <c r="M119" s="5">
         <v>56281</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="O119" s="6">
+        <v>368</v>
+      </c>
+      <c r="O119" s="5">
         <v>47285</v>
       </c>
-    </row>
+      <c r="P119" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T131" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D994</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J994</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I994</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7153,130 +7458,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
